--- a/employee_hours.xlsx
+++ b/employee_hours.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E555"/>
+  <dimension ref="A1:F555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>title</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>firstname</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -477,6 +482,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>keith0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +510,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>donna0</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +538,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>janet1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +566,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lucy0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +594,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rosmarie0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +622,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>kathleen0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +650,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>christopher1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,6 +678,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>david20</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +706,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>john8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,6 +734,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jean1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,6 +762,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jinghao1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -730,6 +790,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>linda4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -753,6 +818,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>kerim0</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -776,6 +846,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>donald0</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -799,6 +874,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jackie0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -822,6 +902,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>bryan2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -845,6 +930,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>todd0</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -868,6 +958,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>jim1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -891,6 +986,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>betty0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -914,6 +1014,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>sharon2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -937,6 +1042,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>darren0</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -960,6 +1070,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>erin1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -983,6 +1098,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>jeremy0</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1006,6 +1126,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>elsa0</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1029,6 +1154,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>david19</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1052,6 +1182,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>rebecca2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1075,6 +1210,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>eric6</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1098,6 +1238,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>judy1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1121,6 +1266,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>peter4</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1144,6 +1294,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>sean4</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1167,6 +1322,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>vamsi1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1190,6 +1350,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>jane2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1213,6 +1378,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>alexander1</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1236,6 +1406,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>margaret1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1259,6 +1434,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>christopher2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1282,6 +1462,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>aidan0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1305,6 +1490,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>james11</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1328,6 +1518,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>michael13</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1351,6 +1546,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>stefan0</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1374,6 +1574,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>james10</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1397,6 +1602,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>eric3</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1420,6 +1630,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>della0</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1443,6 +1658,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>joy0</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1466,6 +1686,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>prashanth0</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1489,6 +1714,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>scott6</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1512,6 +1742,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>jane0</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1535,6 +1770,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>bonnie2</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1558,6 +1798,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>eugene2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1581,6 +1826,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>kirk2</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1604,6 +1854,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>william1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1627,6 +1882,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>andrea1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1650,6 +1910,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>daniel2</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1673,6 +1938,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>scott1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1696,6 +1966,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>elsie0</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1719,6 +1994,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>john14</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1742,6 +2022,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>yale0</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1765,6 +2050,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>phyllis2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1788,6 +2078,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>joseph2</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1811,6 +2106,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>judy3</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1834,6 +2134,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>connie0</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1857,6 +2162,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>paulo0</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1880,6 +2190,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>teanna0</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1903,6 +2218,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>michael16</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1926,6 +2246,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>derek0</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1949,6 +2274,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>jon1</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1972,6 +2302,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ted0</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1995,6 +2330,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>richard1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2018,6 +2358,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>alice1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2041,6 +2386,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>alan1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2064,6 +2414,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>cornelius0</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2087,6 +2442,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>jill1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2110,6 +2470,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>joseph1</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2133,6 +2498,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>lester0</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2156,6 +2526,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>andrew2</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2179,6 +2554,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>randall0</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2202,6 +2582,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>blaine0</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2225,6 +2610,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>luis0</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2248,6 +2638,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>brenda2</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2271,6 +2666,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>gabriele0</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2294,6 +2694,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>rudolph0</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2317,6 +2722,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>michael12</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2340,6 +2750,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>nicky0</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2363,6 +2778,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>michael18</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2386,6 +2806,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>stanley0</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2409,6 +2834,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>yao-qiang0</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2432,6 +2862,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>marjorie0</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2455,6 +2890,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>sandra2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2478,6 +2918,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>hao1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2501,6 +2946,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>jolie0</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2524,6 +2974,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>diane4</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2547,6 +3002,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>payton0</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2570,6 +3030,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>roger1</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2593,6 +3058,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>edna0</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2616,6 +3086,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>a0</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2639,6 +3114,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>jean3</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2662,6 +3142,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ido0</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2685,6 +3170,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>frank5</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2708,6 +3198,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>robert6</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2731,6 +3226,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>josh0</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2754,6 +3254,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>chris6</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2777,6 +3282,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>brian6</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2800,6 +3310,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>robert5</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2823,6 +3338,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>sandra4</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2846,6 +3366,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>vance0</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2869,6 +3394,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>robin0</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2892,6 +3422,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>danielle1</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2915,6 +3450,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>lola0</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2938,6 +3478,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>jodan0</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2961,6 +3506,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>jessie0</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2984,6 +3534,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>bronson0</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3007,6 +3562,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>james12</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3030,6 +3590,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>denean0</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3053,6 +3618,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>erik0</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3076,6 +3646,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>robert4</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3099,6 +3674,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>sunil0</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3122,6 +3702,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>richard4</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3145,6 +3730,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>matthias1</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3168,6 +3758,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>sairaj1</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3191,6 +3786,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>lucio0</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3214,6 +3814,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>beth0</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3237,6 +3842,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>janet2</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3260,6 +3870,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>chris5</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3283,6 +3898,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>michaeljohn0</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3306,6 +3926,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>guy0</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3329,6 +3954,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>frances1</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3352,6 +3982,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>billy0</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3375,6 +4010,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>leo0</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3398,6 +4038,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>grant1</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3421,6 +4066,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>gabriel0</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3444,6 +4094,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>scott3</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3467,6 +4122,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>wayne0</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3490,6 +4150,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>michael11</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3513,6 +4178,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>alberto0</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3536,6 +4206,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>thierry1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3559,6 +4234,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>daniel0</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3582,6 +4262,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>linda9</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3605,6 +4290,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>stephen1</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3628,6 +4318,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>neva0</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3651,6 +4346,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>john6</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3674,6 +4374,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>thomas1</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3697,6 +4402,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>dylan1</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3720,6 +4430,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ben1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3743,6 +4458,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>jacob0</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3766,6 +4486,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ann0</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3789,6 +4514,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>matthew5</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3812,6 +4542,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>virginia0</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3835,6 +4570,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>scott4</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3858,6 +4598,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>robert13</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3881,6 +4626,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>mete0</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3904,6 +4654,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>wanda0</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3927,6 +4682,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>dora0</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3950,6 +4710,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>john10</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3973,6 +4738,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>karren0</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3996,6 +4766,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>abigail0</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4019,6 +4794,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ingrid0</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4042,6 +4822,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>oscar0</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4065,6 +4850,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>shane2</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4088,6 +4878,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>maxwell0</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4111,6 +4906,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>joe1</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4134,6 +4934,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ramona0</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4157,6 +4962,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>sharon1</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4180,6 +4990,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>chris3</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4203,6 +5018,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>jack2</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4226,6 +5046,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>teresa0</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4249,6 +5074,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>tammy0</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4272,6 +5102,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>elizabeth2</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4295,6 +5130,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>bruno0</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4318,6 +5158,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>mary8</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4341,6 +5186,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>kevin4</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4364,6 +5214,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>julie1</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4387,6 +5242,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>robert7</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4410,6 +5270,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>clarence0</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4433,6 +5298,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>john22</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4456,6 +5326,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>victor0</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4479,6 +5354,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>bonnie1</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4502,6 +5382,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>shirley0</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4525,6 +5410,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>peter3</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4548,6 +5438,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>juanita0</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4571,6 +5466,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>eddie0</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4594,6 +5494,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>jean2</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4617,6 +5522,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>greg1</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4640,6 +5550,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>angela1</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4663,6 +5578,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ruth1</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4686,6 +5606,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>lee0</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4709,6 +5634,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>darrell0</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4732,6 +5662,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>anthony0</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4755,6 +5690,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>dirk0</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4778,6 +5718,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>gustavo1</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4801,6 +5746,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>douglas1</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4824,6 +5774,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>lindsey0</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4847,6 +5802,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>james3</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4870,6 +5830,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>cory0</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4893,6 +5858,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>shannon0</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4916,6 +5886,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>jauna0</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4939,6 +5914,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>janainabarreirogambaro0</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4962,6 +5942,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>shaun0</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4985,6 +5970,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>john16</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5008,6 +5998,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>olga0</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5031,6 +6026,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>jon0</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5054,6 +6054,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>gail1</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5077,6 +6082,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>michael15</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5100,6 +6110,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>martha0</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5123,6 +6138,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>glenn0</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5146,6 +6166,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>bob1</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5169,6 +6194,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>janeth1</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5192,6 +6222,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>delia0</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5215,6 +6250,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>john19</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5238,6 +6278,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>kay0</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5261,6 +6306,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>mihail1</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -5284,6 +6334,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>lori2</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5307,6 +6362,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ruth2</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -5330,6 +6390,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>margaret0</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -5353,6 +6418,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>garth0</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5376,6 +6446,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>michael24</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5399,6 +6474,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>marcia0</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5422,6 +6502,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>amy1</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5445,6 +6530,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>kelly0</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -5468,6 +6558,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>brad0</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5491,6 +6586,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>fran�ois1</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5514,6 +6614,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>mary4</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5537,6 +6642,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ryan1</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5560,6 +6670,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>dragan1</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5583,6 +6698,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>thomas2</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5606,6 +6726,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>mary6</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5629,6 +6754,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>david15</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5652,6 +6782,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>diane5</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5675,6 +6810,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>helen2</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5698,6 +6838,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>yuping0</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5721,6 +6866,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>stephen4</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5744,6 +6894,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>willie0</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5767,6 +6922,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>andrew5</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5790,6 +6950,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>rmorgan0</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5813,6 +6978,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>christian1</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5836,6 +7006,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>anton0</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5859,6 +7034,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>samuel0</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5882,6 +7062,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>nkenge0</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5905,6 +7090,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>paul2</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5928,6 +7118,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>marvin0</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5951,6 +7146,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>sean2</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5974,6 +7174,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>richard0</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5997,6 +7202,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>curtis0</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6020,6 +7230,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>cecil0</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6043,6 +7258,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>janice1</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6066,6 +7286,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>carolyn0</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -6089,6 +7314,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>kim2</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6112,6 +7342,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>catherine0</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -6135,6 +7370,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>shanay0</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6158,6 +7398,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>rhoda0</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -6181,6 +7426,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>pat1</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -6204,6 +7454,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>stefano0</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -6227,6 +7482,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>kathie1</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6250,6 +7510,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>bob2</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -6273,6 +7538,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>derik0</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6296,6 +7566,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>vassar0</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6319,6 +7594,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>wathalee0</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6342,6 +7622,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>david16</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6365,6 +7650,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>lizamarie0</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6388,6 +7678,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>arlene0</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -6411,6 +7706,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>matthew3</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6434,6 +7734,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>robert12</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6457,6 +7762,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>phyllis1</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6480,6 +7790,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>mike3</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6503,6 +7818,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>robert8</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6526,6 +7846,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>roger2</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6549,6 +7874,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>rose1</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6572,6 +7902,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>denise1</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6595,6 +7930,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>gregory1</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6618,6 +7958,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>ronald1</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6641,6 +7986,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>michael25</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6664,6 +8014,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ajay0</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6687,6 +8042,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>nieves0</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6710,6 +8070,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>kathy0</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6733,6 +8098,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>patricia0</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6756,6 +8126,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>valerie0</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6779,6 +8154,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>jill2</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6802,6 +8182,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>gerald0</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6825,6 +8210,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>john20</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6848,6 +8238,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>cecelia0</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6871,6 +8266,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>reuben1</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6894,6 +8294,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>linda8</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6917,6 +8322,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>sandra3</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6940,6 +8350,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>bev0</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6963,6 +8378,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>ann2</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6986,6 +8406,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>maciej1</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7009,6 +8434,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>roger0</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7032,6 +8462,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>linda5</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7055,6 +8490,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>catherine0</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7078,6 +8518,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>margaret0</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -7101,6 +8546,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>jay1</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -7124,6 +8574,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>samuel0</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -7147,6 +8602,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>amy1</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7170,6 +8630,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>gregory0</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -7193,6 +8658,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>michelle0</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -7216,6 +8686,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>sean2</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7239,6 +8714,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>cecil0</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7262,6 +8742,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>oscar0</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7285,6 +8770,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>ramona0</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7308,6 +8798,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>tom1</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7331,6 +8826,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>john6</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7354,6 +8854,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>teresa0</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7377,6 +8882,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>robert2</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7400,6 +8910,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>daniel0</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7423,6 +8938,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>james3</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7446,6 +8966,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>wayne0</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7469,6 +8994,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>robert3</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7492,6 +9022,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>josh0</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7515,6 +9050,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>gytis0</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7538,6 +9078,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>shaun0</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7561,6 +9106,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>john8</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7584,6 +9134,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>christopher1</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7607,6 +9162,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>ann0</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7630,6 +9190,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>edna0</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7653,6 +9218,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>john10</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7676,6 +9246,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>matthias1</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7699,6 +9274,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>steven1</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7722,6 +9302,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>jackie0</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7745,6 +9330,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>donald0</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7768,6 +9358,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>linda4</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7791,6 +9386,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>michael11</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7814,6 +9414,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>gabriel0</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7837,6 +9442,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>luis0</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7860,6 +9470,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>randall0</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7883,6 +9498,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>lester0</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7906,6 +9526,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>richard1</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7929,6 +9554,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ted0</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7952,6 +9582,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>alan1</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7975,6 +9610,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>christopher2</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7998,6 +9638,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>john12</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8021,6 +9666,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>willie0</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8044,6 +9694,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>robert5</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -8067,6 +9722,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>mary5</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -8090,6 +9750,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>june0</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8113,6 +9778,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>dirk0</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -8136,6 +9806,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>janainabarreirogambaro0</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8159,6 +9834,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>megan0</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8182,6 +9862,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>karren0</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -8205,6 +9890,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>jared0</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -8228,6 +9918,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>ryan1</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -8251,6 +9946,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>mari0</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -8274,6 +9974,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>barbara2</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -8297,6 +10002,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>joan0</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -8320,6 +10030,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>suzanadeabreu0</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8343,6 +10058,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>carlton0</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8366,6 +10086,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>jane0</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8389,6 +10114,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>jovita0</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8412,6 +10142,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>rosmarie0</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8435,6 +10170,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>raul0</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8458,6 +10198,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>brigid0</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8481,6 +10226,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>stacey0</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8504,6 +10254,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>pei0</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8527,6 +10282,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>nicky0</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8550,6 +10310,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>ruth1</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8573,6 +10338,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>anthony0</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8596,6 +10366,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>jill1</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8619,6 +10394,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>alice1</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8642,6 +10422,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>jane1</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8665,6 +10450,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>connie0</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8688,6 +10478,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>john14</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8711,6 +10506,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>scott1</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8734,6 +10534,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>william1</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8757,6 +10562,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>dorothy0</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8780,6 +10590,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>scott2</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8803,6 +10618,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>eva0</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8826,6 +10646,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>marlin0</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8849,6 +10674,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>grant1</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8872,6 +10702,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>conor0</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8895,6 +10730,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>jacob0</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8918,6 +10758,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>alexander1</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8941,6 +10786,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>aidan0</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8964,6 +10814,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>stefan0</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8987,6 +10842,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>brenda2</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -9010,6 +10870,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>gabriele0</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -9033,6 +10898,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>dick1</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -9056,6 +10926,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>rudolph0</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -9079,6 +10954,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>patricia0</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -9102,6 +10982,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>bart0</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -9125,6 +11010,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>maciej1</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -9148,6 +11038,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>linda5</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -9171,6 +11066,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>shannon0</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -9194,6 +11094,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>jauna0</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -9217,6 +11122,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>terry1</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -9240,6 +11150,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>john16</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -9263,6 +11178,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>mark2</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -9286,6 +11206,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>janeth1</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -9309,6 +11234,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>twanna0</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9332,6 +11262,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>ann1</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -9355,6 +11290,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>john17</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9378,6 +11318,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>carolyn0</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9401,6 +11346,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>geri0</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9424,6 +11374,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>rhoda0</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9447,6 +11402,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>kathie1</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9470,6 +11430,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>garth0</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9493,6 +11458,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>dorothy1</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -9516,6 +11486,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>mihail1</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -9539,6 +11514,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>john19</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -9562,6 +11542,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>paul3</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9585,6 +11570,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>bob1</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -9608,6 +11598,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>michael15</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -9631,6 +11626,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>jon0</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -9654,6 +11654,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>kathleen0</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -9677,6 +11682,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>dominic0</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9700,6 +11710,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>janet1</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9723,6 +11738,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>leo0</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9746,6 +11766,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>frances1</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9769,6 +11794,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>janet2</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9792,6 +11822,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>mary6</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9815,6 +11850,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>scott4</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9838,6 +11878,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>mete0</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9861,6 +11906,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>brian4</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9884,6 +11934,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>abigail0</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9907,6 +11962,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>derek0</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9930,6 +11990,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>jon1</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9953,6 +12018,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>douglas2</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9976,6 +12046,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>erin1</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9999,6 +12074,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>betty0</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -10022,6 +12102,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>bryan2</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -10045,6 +12130,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>kerim0</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -10068,6 +12158,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>jean1</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -10091,6 +12186,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>katherine0</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -10114,6 +12214,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>lucy0</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -10137,6 +12242,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>roger0</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -10160,6 +12270,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>ann2</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -10183,6 +12298,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>james8</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -10206,6 +12326,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>brenda3</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -10229,6 +12354,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>john20</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -10252,6 +12382,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>valerie0</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -10275,6 +12410,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>irene0</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -10298,6 +12438,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>cheryl0</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -10321,6 +12466,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>ronald1</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -10344,6 +12494,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>andrew4</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -10367,6 +12522,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>helge0</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -10390,6 +12550,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>eddie0</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -10413,6 +12578,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>juanita0</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -10436,6 +12606,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>peter3</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -10459,6 +12634,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>curtis0</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -10482,6 +12662,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>janice1</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -10505,6 +12690,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>joshua0</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -10528,6 +12718,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>arlene0</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -10551,6 +12746,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>phyllis1</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -10574,6 +12774,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>ryan4</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -10597,6 +12802,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>beth0</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -10620,6 +12830,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>lucio0</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -10643,6 +12858,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>erik0</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -10666,6 +12886,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>denean0</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -10689,6 +12914,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>bronson0</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -10712,6 +12942,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>jodan0</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10735,6 +12970,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>mary7</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10758,6 +12998,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>vance0</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10781,6 +13026,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>joyce0</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10804,6 +13054,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>stephen3</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10827,6 +13082,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>danielle1</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10850,6 +13110,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>barry1</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10873,6 +13138,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>brian6</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10896,6 +13166,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>david18</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10919,6 +13194,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>jean3</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10942,6 +13222,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>peggy0</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10965,6 +13250,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>sandeep1</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10988,6 +13278,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>lori2</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -11011,6 +13306,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>victor0</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -11034,6 +13334,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>john22</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -11057,6 +13362,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>elizabeth2</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -11080,6 +13390,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>karan1</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -11103,6 +13418,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>joe1</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -11126,6 +13446,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>shane2</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -11149,6 +13474,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>tim0</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -11172,6 +13502,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>anton0</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -11195,6 +13530,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>christian1</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -11218,6 +13558,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>andrew5</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -11241,6 +13586,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>kirk2</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -11264,6 +13614,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>eugene2</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -11287,6 +13642,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>scott6</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -11310,6 +13670,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>joy0</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -11333,6 +13698,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>mitch0</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -11356,6 +13726,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>deepak0</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -11379,6 +13754,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>vamsi1</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -11402,6 +13782,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>peter4</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -11425,6 +13810,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>rebecca2</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -11448,6 +13838,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>elsa0</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -11471,6 +13866,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>michael18</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -11494,6 +13894,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>marjorie0</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -11517,6 +13922,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>frank4</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -11540,6 +13950,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>mark5</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -11563,6 +13978,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>jolie0</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -11586,6 +14006,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>a0</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -11609,6 +14034,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>bonnie2</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -11632,6 +14062,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>elsie0</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -11655,6 +14090,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>george3</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -11678,6 +14118,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>yale0</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -11701,6 +14146,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>yuhong1</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -11724,6 +14174,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>joseph2</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -11747,6 +14202,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>david20</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -11770,6 +14230,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>jinghao1</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11793,6 +14258,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>kevin5</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11816,6 +14286,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>judy1</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11839,6 +14314,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>denise1</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -11862,6 +14342,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>scott7</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11885,6 +14370,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>walter1</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11908,6 +14398,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>ajay0</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11931,6 +14426,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>tomas0</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11954,6 +14454,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>melissa0</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11977,6 +14482,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>linda8</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -12000,6 +14510,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>frank5</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -12023,6 +14538,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>steve2</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -12046,6 +14566,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>jennifer1</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -12069,6 +14594,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>chris6</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -12092,6 +14622,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>sandra4</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -12115,6 +14650,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>robin0</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -12138,6 +14678,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>jane3</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -12161,6 +14706,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>james12</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -12184,6 +14734,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>yvonne1</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -12207,6 +14762,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>nancy3</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -12230,6 +14790,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>raquel0</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -12253,6 +14818,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>rmorgan0</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -12276,6 +14846,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>stephen4</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -12299,6 +14874,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>virginia0</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -12322,6 +14902,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>matthew5</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -12345,6 +14930,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>ben1</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -12368,6 +14958,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>neva0</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -12391,6 +14986,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>linda9</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -12414,6 +15014,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>laura3</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -12437,6 +15042,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>shanay0</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -12460,6 +15070,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>derik0</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -12483,6 +15098,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>vassar0</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -12506,6 +15126,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>wathalee0</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -12529,6 +15154,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>alice4</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -12552,6 +15182,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>jim5</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -12575,6 +15210,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>robert12</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -12598,6 +15238,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>rubysue0</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -12621,6 +15266,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>elizabeth4</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -12644,6 +15294,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>michael24</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -12667,6 +15322,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>marcia0</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -12690,6 +15350,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>krishna1</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -12713,6 +15378,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>brad0</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -12736,6 +15406,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>katherine1</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -12759,6 +15434,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>julie1</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -12782,6 +15462,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>mike6</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -12805,6 +15490,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>chad1</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -12828,6 +15518,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>judy3</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -12851,6 +15546,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>phyllis2</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -12874,6 +15574,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>daniel2</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -12897,6 +15602,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>andrea1</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -12920,6 +15630,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>diane5</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -12943,6 +15658,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>glenn0</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -12966,6 +15686,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>billy0</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -12989,6 +15714,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>christie0</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -13012,6 +15742,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>phyllis3</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -13035,6 +15770,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>sairaj1</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -13058,6 +15798,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>roger2</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -13081,6 +15826,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>gregory1</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -13104,6 +15854,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>michael25</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -13127,6 +15882,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>margaret2</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -13150,6 +15910,11 @@
           <t>sales rep</t>
         </is>
       </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>gary6</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -13173,6 +15938,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>patricia2</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -13194,6 +15964,11 @@
       <c r="E555" t="inlineStr">
         <is>
           <t>sales rep</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>raja0</t>
         </is>
       </c>
     </row>
